--- a/balance/source/battle-balance.xlsx
+++ b/balance/source/battle-balance.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="1" r:id="R3957c155ae654c17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawnSpec" sheetId="2" r:id="Rccf87866aca74a7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPatternSpec" sheetId="3" r:id="R462cfcb4f8d04ba5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillSpec" sheetId="4" r:id="R069b4ece98dc4efa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSkillLink" sheetId="5" r:id="R183ce2ffd5de41a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProjectileSpec" sheetId="6" r:id="R1860084022af4c9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillEffectSpec" sheetId="7" r:id="R4635f47eccf14f5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="1" r:id="R066b83929cfa4e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawnSpec" sheetId="2" r:id="Rdd99b33b5b3d4eb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPatternSpec" sheetId="3" r:id="R64b53e9826094ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillSpec" sheetId="4" r:id="Re6b37738f2364fe6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSkillLink" sheetId="5" r:id="R634b46bbc21f4481"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProjectileSpec" sheetId="6" r:id="R5a2f64a36c194c70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillEffectSpec" sheetId="7" r:id="R1f6453f9d9d740ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,7 +23,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.0"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -34,8 +34,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -47,8 +52,13 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="4">
+  <x:borders count="16">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -80,11 +90,119 @@
         <x:color rgb="FF163A5C"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="51">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -134,6 +252,133 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -915,7 +1160,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44d75af3b856458a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2f0f822a0f0425a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1552,7 +1797,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45df14574d2d4b01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra26872f0695849fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1616,7 +1861,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e6f9854028640a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d0d49cf9cae4743"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1625,24 +1870,24 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16.75" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.75" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15.5" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.75" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="13.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11.5" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="8" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="9.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="str">
         <x:v>skillId</x:v>
       </x:c>
@@ -1687,6 +1932,53 @@
       </x:c>
       <x:c r="O1" s="11" t="str">
         <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="26" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="B2" s="27" t="str">
+        <x:v>skill.basic.name</x:v>
+      </x:c>
+      <x:c r="C2" s="27" t="str">
+        <x:v>skill.basic.description</x:v>
+      </x:c>
+      <x:c r="D2" s="27" t="str">
+        <x:v>BASIC_ATTACK</x:v>
+      </x:c>
+      <x:c r="E2" s="27" t="str">
+        <x:v>BASIC_ATTACK</x:v>
+      </x:c>
+      <x:c r="F2" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H2" s="27" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I2" s="27" t="str">
+        <x:v>DEFAULT_PROGRESS</x:v>
+      </x:c>
+      <x:c r="J2" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K2" s="27" t="str">
+        <x:v>PROJ_BASIC</x:v>
+      </x:c>
+      <x:c r="L2" s="27" t="str">
+        <x:v>BasicAttack</x:v>
+      </x:c>
+      <x:c r="M2" s="27" t="str">
+        <x:v>BasicProjectile</x:v>
+      </x:c>
+      <x:c r="N2" s="27" t="str">
+        <x:v>BasicHit</x:v>
+      </x:c>
+      <x:c r="O2" s="28" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1703,7 +1995,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3731570854d64f30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc38497d870d942ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1712,14 +2004,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8.25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.75" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="str">
         <x:v>alienId</x:v>
       </x:c>
@@ -1734,12 +2026,828 @@
       </x:c>
       <x:c r="E1" s="11" t="str">
         <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="39" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C2" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2" s="40" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C3" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D3" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E3" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C4" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E4" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C5" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C6" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="41" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C7" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C8" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="41" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C9" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="41" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C10" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="41" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C11" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="41" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C12" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="41" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C13" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="41" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C14" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="41" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C15" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C16" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="41" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C17" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="41" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C18" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="41" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C19" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="41" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C20" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="41" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C21" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="41" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C22" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="41" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C23" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="41" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B24" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C24" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="41" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B25" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C25" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="41" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C26" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
+      <x:c r="A27" s="41" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B27" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C27" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
+      <x:c r="A28" s="41" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B28" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C28" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
+      <x:c r="A29" s="41" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B29" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C29" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="15" hidden="0" customHeight="1">
+      <x:c r="A30" s="41" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B30" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C30" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E30" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
+      <x:c r="A31" s="41" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B31" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C31" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E31" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
+      <x:c r="A32" s="41" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B32" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C32" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E32" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
+      <x:c r="A33" s="41" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B33" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C33" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E33" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
+      <x:c r="A34" s="41" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B34" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C34" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
+      <x:c r="A35" s="41" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B35" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C35" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="41" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B36" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C36" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
+      <x:c r="A37" s="41" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B37" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C37" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
+      <x:c r="A38" s="41" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C38" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
+      <x:c r="A39" s="41" t="n">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C39" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
+      <x:c r="A40" s="41" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C40" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
+      <x:c r="A41" s="41" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C41" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E41" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
+      <x:c r="A42" s="41" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C42" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E42" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
+      <x:c r="A43" s="41" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C43" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E43" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
+      <x:c r="A44" s="41" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C44" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E44" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
+      <x:c r="A45" s="41" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B45" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C45" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D45" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E45" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
+      <x:c r="A46" s="41" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C46" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D46" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E46" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
+      <x:c r="A47" s="41" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B47" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C47" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D47" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E47" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="15" hidden="0" customHeight="1">
+      <x:c r="A48" s="41" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B48" s="42" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C48" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D48" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E48" s="43" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="15" hidden="0" customHeight="1">
+      <x:c r="A49" s="44" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B49" s="45" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="C49" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D49" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E49" s="46" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R028e672b2e6b4f8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b68d0840c004e00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1748,19 +2856,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12.25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="9.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="str">
         <x:v>projectileId</x:v>
       </x:c>
@@ -1790,6 +2898,38 @@
       </x:c>
       <x:c r="J1" s="11" t="str">
         <x:v>enabled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="26" t="str">
+        <x:v>PROJ_BASIC</x:v>
+      </x:c>
+      <x:c r="B2" s="27" t="str">
+        <x:v>BattleProjectile</x:v>
+      </x:c>
+      <x:c r="C2" s="27" t="str">
+        <x:v>HOMING</x:v>
+      </x:c>
+      <x:c r="D2" s="27" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E2" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="27" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="G2" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H2" s="48" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I2" s="27" t="str">
+        <x:v>DESTROY</x:v>
+      </x:c>
+      <x:c r="J2" s="28" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1803,7 +2943,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f0a75633a1744a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb2d31f15c3b474c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1812,23 +2952,23 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="29" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="19" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="17" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="19" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="27.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.75" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="7.75" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="11" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14.130000114440918" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
       <x:c r="A1" s="9" t="str">
         <x:v>skillId</x:v>
       </x:c>
@@ -1870,6 +3010,50 @@
       </x:c>
       <x:c r="N1" s="11" t="str">
         <x:v>bossMultiplier</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="26" t="str">
+        <x:v>SKILL_BASIC</x:v>
+      </x:c>
+      <x:c r="B2" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="27" t="str">
+        <x:v>ON_HIT</x:v>
+      </x:c>
+      <x:c r="D2" s="27" t="str">
+        <x:v>DAMAGE</x:v>
+      </x:c>
+      <x:c r="E2" s="27" t="str">
+        <x:v>ATTACK_SNAPSHOT_DAMAGE</x:v>
+      </x:c>
+      <x:c r="F2" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I2" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K2" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L2" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M2" s="27" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="N2" s="50" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1889,7 +3073,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb450ac58985348a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbefe05d145cb40c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/balance/source/battle-balance.xlsx
+++ b/balance/source/battle-balance.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="1" r:id="R066b83929cfa4e3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawnSpec" sheetId="2" r:id="Rdd99b33b5b3d4eb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPatternSpec" sheetId="3" r:id="R64b53e9826094ee3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillSpec" sheetId="4" r:id="Re6b37738f2364fe6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSkillLink" sheetId="5" r:id="R634b46bbc21f4481"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProjectileSpec" sheetId="6" r:id="R5a2f64a36c194c70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillEffectSpec" sheetId="7" r:id="R1f6453f9d9d740ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpec" sheetId="1" r:id="Ra025a136e6a34e14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WaveSpawnSpec" sheetId="2" r:id="R3a25788dfadb414f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossPatternSpec" sheetId="3" r:id="Rcd6897c6863142c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillSpec" sheetId="4" r:id="Rf388d1829a73465c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlienSkillLink" sheetId="5" r:id="R620bffb44e314909"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProjectileSpec" sheetId="6" r:id="Rf0d9af1a5ef946b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillEffectSpec" sheetId="7" r:id="Rdbb4a2db1bd140cc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.0"/>
+    <x:numFmt numFmtId="202" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -202,7 +203,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="51">
+  <x:cellXfs count="53">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -379,6 +380,14 @@
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1160,7 +1169,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2f0f822a0f0425a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3502752b1201495f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1797,7 +1806,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra26872f0695849fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd365055fd5fc4034"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1850,6 +1859,66 @@
         <x:v>enabled</x:v>
       </x:c>
     </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>WAVE_010</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>SET_PHASE</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>ON_SPAWN</x:v>
+      </x:c>
+      <x:c r="E2" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" t="str"/>
+      <x:c r="H2" t="str">
+        <x:v>phase</x:v>
+      </x:c>
+      <x:c r="I2" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="52" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>WAVE_010</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>SET_MOVE_SPEED_MULTIPLIER</x:v>
+      </x:c>
+      <x:c r="D3" t="str">
+        <x:v>HP_PERCENT</x:v>
+      </x:c>
+      <x:c r="E3" s="51" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F3" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G3" t="str"/>
+      <x:c r="H3" t="str">
+        <x:v>moveSpeedMultiplier</x:v>
+      </x:c>
+      <x:c r="I3" s="51" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+      <x:c r="J3" s="52" t="b">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="C2:C200">
@@ -1861,7 +1930,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d0d49cf9cae4743"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff87ea8fcc0a48b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1995,7 +2064,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc38497d870d942ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd38c3f62505c4e6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2847,7 +2916,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b68d0840c004e00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70ee9ae6538e4e4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2943,7 +3012,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb2d31f15c3b474c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4c135269e47485d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3073,7 +3142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbefe05d145cb40c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4ccda84dcc04bdd"/>
   </x:tableParts>
 </x:worksheet>
 </file>